--- a/duoki_editor/resources/data/blank/餐厅-一般疑问句_问句跟读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/餐厅-一般疑问句_问句跟读-1-blank.xlsx
@@ -109,7 +109,7 @@
     <t>哇，{npc2_name}来了呀！欢迎光临！快看，我们餐厅今天有超级神奇的魔法菜品哟！{sentence_question_cn}？{sentence_question_en}?</t>
   </si>
   <si>
-    <t>如果不喜欢吃该说什么呢？</t>
+    <t>如果不喜欢吃该说什么呢？{sentence_question_cn}？{sentence_question_en}?</t>
   </si>
   <si>
     <t>{sentence_answer_en_1}。 {sentence_answer_cn_1} 。</t>
